--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/mar-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>608.5586</v>
+        <v>26642.7</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>172.039</v>
+        <v>7531.87</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>641.9</v>
+        <v>28102.38</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>321.1</v>
+        <v>14057.76</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1680</v>
+        <v>73550.39999999999</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>531.03</v>
+        <v>23248.49</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>599.76</v>
+        <v>26257.49</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4995.6</v>
+        <v>218707.38</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>471.38</v>
+        <v>20637.02</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>181.257</v>
+        <v>7935.43</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4287.92</v>
+        <v>187725.15</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>585.528</v>
+        <v>25634.42</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>811.4400000000001</v>
+        <v>35524.85</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2839.74</v>
+        <v>124323.82</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2002</v>
+        <v>87647.56</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1313.28</v>
+        <v>57495.4</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1518</v>
+        <v>66458.03999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>926.21</v>
+        <v>40549.48</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1061.18</v>
+        <v>46458.46</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1415.4016</v>
+        <v>61966.29</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>313.4705</v>
+        <v>13723.74</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>738.8232</v>
+        <v>32345.68</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>699.4344</v>
+        <v>30621.24</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>171.12</v>
+        <v>7491.63</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1272.6206</v>
+        <v>55715.33</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1662.5</v>
+        <v>72784.25</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>251.1</v>
+        <v>10993.16</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>358.7682</v>
+        <v>15706.87</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>349.86</v>
+        <v>15316.87</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>427.8</v>
+        <v>18729.09</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1344</v>
+        <v>58840.32</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1279.5176</v>
+        <v>56017.28</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>39348</v>
+        <v>1722655.54</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1581.9768</v>
+        <v>69258.95</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>202.762</v>
+        <v>8876.92</v>
       </c>
     </row>
     <row r="37">
@@ -2704,11 +2704,11 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>109.48</v>
+        <v>4793.03</v>
       </c>
     </row>
     <row r="38">
@@ -2765,11 +2765,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>691.6</v>
+        <v>30278.25</v>
       </c>
     </row>
     <row r="39">
@@ -2826,11 +2826,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1678.08</v>
+        <v>73466.35000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2887,11 +2887,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1152</v>
+        <v>50434.56</v>
       </c>
     </row>
     <row r="41">
@@ -2948,11 +2948,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>188.94</v>
+        <v>8271.790000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3009,11 +3009,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>739.7536</v>
+        <v>32386.41</v>
       </c>
     </row>
     <row r="43">
@@ -3070,11 +3070,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1002.174</v>
+        <v>43875.18</v>
       </c>
     </row>
     <row r="44">
@@ -3131,11 +3131,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>454.72</v>
+        <v>19907.64</v>
       </c>
     </row>
     <row r="45">
@@ -3192,11 +3192,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>460.75</v>
+        <v>20171.64</v>
       </c>
     </row>
     <row r="46">
@@ -3253,11 +3253,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1442.56</v>
+        <v>63155.28</v>
       </c>
     </row>
     <row r="47">
@@ -3314,11 +3314,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>758.88</v>
+        <v>33223.77</v>
       </c>
     </row>
     <row r="48">
@@ -3375,11 +3375,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>201.3729</v>
+        <v>8816.110000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3436,11 +3436,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1041.9304</v>
+        <v>45615.72</v>
       </c>
     </row>
     <row r="50">
@@ -3497,11 +3497,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>757.15</v>
+        <v>33148.03</v>
       </c>
     </row>
   </sheetData>
